--- a/crates/xlstream-eval/tests/fixtures/logical/if_ifs_switch.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/logical/if_ifs_switch.xlsx
@@ -20,27 +20,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
-  <si>
-    <t xml:space="preserve">id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+  <si>
+    <t xml:space="preserve">val</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
   </si>
   <si>
-    <t xml:space="preserve">true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch</t>
+    <t xml:space="preserve">if_gt50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if_nested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifs_multi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">switch_region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">switch_default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if_bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if_zero</t>
   </si>
   <si>
     <t xml:space="preserve">EMEA</t>
@@ -50,6 +56,9 @@
   </si>
   <si>
     <t xml:space="preserve">AMER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LATAM</t>
   </si>
 </sst>
 </file>
@@ -125,11 +134,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -326,7 +331,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -351,89 +356,119 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="str">
+        <v>9</v>
+      </c>
+      <c r="C2" s="0" t="str">
         <f aca="false">IF(A2&gt;50,"high","low")</f>
         <v>low</v>
       </c>
-      <c r="F2" s="0" t="str">
+      <c r="D2" s="0" t="str">
+        <f aca="false">IF(A2&gt;100,"A",IF(A2&gt;50,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="E2" s="0" t="str">
         <f aca="false">_xlfn.IFS(A2&gt;100,"A",A2&gt;50,"B",A2&gt;0,"C",TRUE(),"D")</f>
         <v>C</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="F2" s="0" t="n">
         <f aca="false">_xlfn.SWITCH(B2,"EMEA",1,"APAC",2,"AMER",3,0)</f>
         <v>1</v>
       </c>
+      <c r="G2" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B2,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="0" t="str">
+        <f aca="false">IF(A2,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I2" s="0" t="str">
+        <f aca="false">IF(A2=0,"zero","nonzero")</f>
+        <v>nonzero</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="str">
+        <v>10</v>
+      </c>
+      <c r="C3" s="0" t="str">
         <f aca="false">IF(A3&gt;50,"high","low")</f>
         <v>low</v>
       </c>
-      <c r="F3" s="0" t="str">
+      <c r="D3" s="0" t="str">
+        <f aca="false">IF(A3&gt;100,"A",IF(A3&gt;50,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="E3" s="0" t="str">
         <f aca="false">_xlfn.IFS(A3&gt;100,"A",A3&gt;50,"B",A3&gt;0,"C",TRUE(),"D")</f>
         <v>C</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="F3" s="0" t="n">
         <f aca="false">_xlfn.SWITCH(B3,"EMEA",1,"APAC",2,"AMER",3,0)</f>
         <v>2</v>
       </c>
+      <c r="G3" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B3,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="str">
+        <f aca="false">IF(A3,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I3" s="0" t="str">
+        <f aca="false">IF(A3=0,"zero","nonzero")</f>
+        <v>nonzero</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C4" s="0" t="str">
+        <f aca="false">IF(A4&gt;50,"high","low")</f>
+        <v>high</v>
+      </c>
+      <c r="D4" s="0" t="str">
+        <f aca="false">IF(A4&gt;100,"A",IF(A4&gt;50,"B","C"))</f>
+        <v>B</v>
       </c>
       <c r="E4" s="0" t="str">
-        <f aca="false">IF(A4&gt;50,"high","low")</f>
-        <v>low</v>
-      </c>
-      <c r="F4" s="0" t="str">
         <f aca="false">_xlfn.IFS(A4&gt;100,"A",A4&gt;50,"B",A4&gt;0,"C",TRUE(),"D")</f>
-        <v>D</v>
-      </c>
-      <c r="G4" s="0" t="n">
+        <v>B</v>
+      </c>
+      <c r="F4" s="0" t="n">
         <f aca="false">_xlfn.SWITCH(B4,"EMEA",1,"APAC",2,"AMER",3,0)</f>
         <v>3</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B4,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="str">
+        <f aca="false">IF(A4,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I4" s="0" t="str">
+        <f aca="false">IF(A4=0,"zero","nonzero")</f>
+        <v>nonzero</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -441,111 +476,143 @@
         <v>100</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="str">
+        <v>9</v>
+      </c>
+      <c r="C5" s="0" t="str">
         <f aca="false">IF(A5&gt;50,"high","low")</f>
         <v>high</v>
       </c>
-      <c r="F5" s="0" t="str">
+      <c r="D5" s="0" t="str">
+        <f aca="false">IF(A5&gt;100,"A",IF(A5&gt;50,"B","C"))</f>
+        <v>B</v>
+      </c>
+      <c r="E5" s="0" t="str">
         <f aca="false">_xlfn.IFS(A5&gt;100,"A",A5&gt;50,"B",A5&gt;0,"C",TRUE(),"D")</f>
         <v>B</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="F5" s="0" t="n">
         <f aca="false">_xlfn.SWITCH(B5,"EMEA",1,"APAC",2,"AMER",3,0)</f>
         <v>1</v>
       </c>
+      <c r="G5" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B5,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="str">
+        <f aca="false">IF(A5,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I5" s="0" t="str">
+        <f aca="false">IF(A5=0,"zero","nonzero")</f>
+        <v>nonzero</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="str">
+        <v>12</v>
+      </c>
+      <c r="C6" s="0" t="str">
         <f aca="false">IF(A6&gt;50,"high","low")</f>
         <v>low</v>
       </c>
-      <c r="F6" s="0" t="str">
+      <c r="D6" s="0" t="str">
+        <f aca="false">IF(A6&gt;100,"A",IF(A6&gt;50,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="E6" s="0" t="str">
         <f aca="false">_xlfn.IFS(A6&gt;100,"A",A6&gt;50,"B",A6&gt;0,"C",TRUE(),"D")</f>
         <v>D</v>
       </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B6,"EMEA",1,"APAC",2,"AMER",3,0)</f>
+        <v>0</v>
+      </c>
       <c r="G6" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH(B6,"EMEA",1,"APAC",2,"AMER",3,0)</f>
-        <v>2</v>
+        <f aca="false">_xlfn.SWITCH(B6,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="str">
+        <f aca="false">IF(A6,"yes","no")</f>
+        <v>no</v>
+      </c>
+      <c r="I6" s="0" t="str">
+        <f aca="false">IF(A6=0,"zero","nonzero")</f>
+        <v>zero</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>-5</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="str">
+        <v>10</v>
+      </c>
+      <c r="C7" s="0" t="str">
         <f aca="false">IF(A7&gt;50,"high","low")</f>
         <v>low</v>
       </c>
-      <c r="F7" s="0" t="str">
+      <c r="D7" s="0" t="str">
+        <f aca="false">IF(A7&gt;100,"A",IF(A7&gt;50,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="E7" s="0" t="str">
         <f aca="false">_xlfn.IFS(A7&gt;100,"A",A7&gt;50,"B",A7&gt;0,"C",TRUE(),"D")</f>
-        <v>C</v>
+        <v>D</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B7,"EMEA",1,"APAC",2,"AMER",3,0)</f>
+        <v>2</v>
       </c>
       <c r="G7" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH(B7,"EMEA",1,"APAC",2,"AMER",3,0)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.SWITCH(B7,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="0" t="str">
+        <f aca="false">IF(A7,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I7" s="0" t="str">
+        <f aca="false">IF(A7=0,"zero","nonzero")</f>
+        <v>nonzero</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="str">
+        <v>11</v>
+      </c>
+      <c r="C8" s="0" t="str">
         <f aca="false">IF(A8&gt;50,"high","low")</f>
         <v>high</v>
       </c>
-      <c r="F8" s="0" t="str">
+      <c r="D8" s="0" t="str">
+        <f aca="false">IF(A8&gt;100,"A",IF(A8&gt;50,"B","C"))</f>
+        <v>A</v>
+      </c>
+      <c r="E8" s="0" t="str">
         <f aca="false">_xlfn.IFS(A8&gt;100,"A",A8&gt;50,"B",A8&gt;0,"C",TRUE(),"D")</f>
-        <v>B</v>
+        <v>A</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B8,"EMEA",1,"APAC",2,"AMER",3,0)</f>
+        <v>3</v>
       </c>
       <c r="G8" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH(B8,"EMEA",1,"APAC",2,"AMER",3,0)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.SWITCH(B8,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="str">
+        <f aca="false">IF(A8,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I8" s="0" t="str">
+        <f aca="false">IF(A8=0,"zero","nonzero")</f>
+        <v>nonzero</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -553,83 +620,107 @@
         <v>1</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="str">
+        <v>9</v>
+      </c>
+      <c r="C9" s="0" t="str">
         <f aca="false">IF(A9&gt;50,"high","low")</f>
         <v>low</v>
       </c>
-      <c r="F9" s="0" t="str">
+      <c r="D9" s="0" t="str">
+        <f aca="false">IF(A9&gt;100,"A",IF(A9&gt;50,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="E9" s="0" t="str">
         <f aca="false">_xlfn.IFS(A9&gt;100,"A",A9&gt;50,"B",A9&gt;0,"C",TRUE(),"D")</f>
         <v>C</v>
       </c>
+      <c r="F9" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B9,"EMEA",1,"APAC",2,"AMER",3,0)</f>
+        <v>1</v>
+      </c>
       <c r="G9" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH(B9,"EMEA",1,"APAC",2,"AMER",3,0)</f>
-        <v>2</v>
+        <f aca="false">_xlfn.SWITCH(B9,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="str">
+        <f aca="false">IF(A9,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I9" s="0" t="str">
+        <f aca="false">IF(A9=0,"zero","nonzero")</f>
+        <v>nonzero</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>999</v>
+        <v>49</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="C10" s="0" t="str">
+        <f aca="false">IF(A10&gt;50,"high","low")</f>
+        <v>low</v>
+      </c>
+      <c r="D10" s="0" t="str">
+        <f aca="false">IF(A10&gt;100,"A",IF(A10&gt;50,"B","C"))</f>
+        <v>C</v>
+      </c>
+      <c r="E10" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A10&gt;100,"A",A10&gt;50,"B",A10&gt;0,"C",TRUE(),"D")</f>
+        <v>C</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B10,"EMEA",1,"APAC",2,"AMER",3,0)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="str">
-        <f aca="false">IF(A10&gt;50,"high","low")</f>
-        <v>high</v>
-      </c>
-      <c r="F10" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A10&gt;100,"A",A10&gt;50,"B",A10&gt;0,"C",TRUE(),"D")</f>
-        <v>A</v>
-      </c>
       <c r="G10" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH(B10,"EMEA",1,"APAC",2,"AMER",3,0)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.SWITCH(B10,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="str">
+        <f aca="false">IF(A10,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I10" s="0" t="str">
+        <f aca="false">IF(A10=0,"zero","nonzero")</f>
+        <v>nonzero</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C11" s="0" t="str">
+        <f aca="false">IF(A11&gt;50,"high","low")</f>
+        <v>high</v>
+      </c>
+      <c r="D11" s="0" t="str">
+        <f aca="false">IF(A11&gt;100,"A",IF(A11&gt;50,"B","C"))</f>
+        <v>B</v>
       </c>
       <c r="E11" s="0" t="str">
-        <f aca="false">IF(A11&gt;50,"high","low")</f>
-        <v>low</v>
-      </c>
-      <c r="F11" s="0" t="str">
         <f aca="false">_xlfn.IFS(A11&gt;100,"A",A11&gt;50,"B",A11&gt;0,"C",TRUE(),"D")</f>
-        <v>C</v>
+        <v>B</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH(B11,"EMEA",1,"APAC",2,"AMER",3,0)</f>
+        <v>2</v>
       </c>
       <c r="G11" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH(B11,"EMEA",1,"APAC",2,"AMER",3,0)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.SWITCH(B11,"XXX",99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="0" t="str">
+        <f aca="false">IF(A11,"yes","no")</f>
+        <v>yes</v>
+      </c>
+      <c r="I11" s="0" t="str">
+        <f aca="false">IF(A11=0,"zero","nonzero")</f>
+        <v>nonzero</v>
       </c>
     </row>
   </sheetData>
